--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Content</t>
   </si>
@@ -53,6 +53,18 @@
   </si>
   <si>
     <t>2h</t>
+  </si>
+  <si>
+    <t>1_differentiation\Part B Implicit Differentiation and Inverse Functions problemset</t>
+  </si>
+  <si>
+    <t>1.5h</t>
+  </si>
+  <si>
+    <t>2. Applications of Differentiation\Part A Approximation and Curve Sketching session23-session28</t>
+  </si>
+  <si>
+    <t>2. Applications of Differentiation\Part A Approximation and Curve Sketching problemset</t>
   </si>
 </sst>
 </file>
@@ -983,8 +995,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="B1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="111.727272727273" customWidth="1"/>
@@ -1020,6 +1032,30 @@
       </c>
       <c r="C4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
